--- a/models/xls/MedicationLine.xlsx
+++ b/models/xls/MedicationLine.xlsx
@@ -505,7 +505,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -941,23 +940,11 @@
           <t>Data Element</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Common Glossary</t>
         </is>
       </c>
-      <c r="O1" s="1" t="n"/>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Example Value</t>
@@ -1078,6 +1065,16 @@
           <t>*</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BusinessIdentifier</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1113,6 +1110,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>RecordedDate</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1148,6 +1155,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Recorder</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1183,6 +1200,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1223,6 +1250,16 @@
           <t>preferred</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1303,6 +1340,16 @@
           <t>required</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>equivalent</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1866,6 +1913,16 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>*</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>equivalent</t>
         </is>
       </c>
     </row>
